--- a/data/sales-tracker.xlsx
+++ b/data/sales-tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/realdekings/Documents/Youtube_Video/Dataset/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/realdekings/Documents/Projects/data-engineering/small-business-sales-tracker-pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9900D8D1-4EC3-B046-898C-392479A3FB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47518805-88DA-5D44-ADD5-5E4CC499B7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="600">
   <si>
     <t>Order ID</t>
   </si>
@@ -1785,6 +1785,54 @@
   </si>
   <si>
     <t>100500</t>
+  </si>
+  <si>
+    <t>$15.00</t>
+  </si>
+  <si>
+    <t>$105.00</t>
+  </si>
+  <si>
+    <t>$25.00</t>
+  </si>
+  <si>
+    <t>$145.00</t>
+  </si>
+  <si>
+    <t>$1,305.00</t>
+  </si>
+  <si>
+    <t>$10.00</t>
+  </si>
+  <si>
+    <t>$80.00</t>
+  </si>
+  <si>
+    <t>$9.99</t>
+  </si>
+  <si>
+    <t>$79.92</t>
+  </si>
+  <si>
+    <t>$65.00</t>
+  </si>
+  <si>
+    <t>$390.00</t>
+  </si>
+  <si>
+    <t>$99.00</t>
+  </si>
+  <si>
+    <t>$495.00</t>
+  </si>
+  <si>
+    <t>$135.00</t>
+  </si>
+  <si>
+    <t>$42.00</t>
+  </si>
+  <si>
+    <t>$168.00</t>
   </si>
 </sst>
 </file>
@@ -1835,7 +1883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1843,6 +1891,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1861,8 +1915,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SalesTrackerTable" displayName="SalesTrackerTable" ref="A1:I501">
-  <autoFilter ref="A1:I501" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SalesTrackerTable" displayName="SalesTrackerTable" ref="A1:I511">
+  <autoFilter ref="A1:I511" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Order ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Order Date"/>
@@ -2054,7 +2108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I501"/>
+  <dimension ref="A1:I511"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -15563,7 +15617,7 @@
         <v>9</v>
       </c>
       <c r="I450" s="3">
-        <f t="shared" ref="I450:I513" si="7">G450*H450</f>
+        <f t="shared" ref="I450:I501" si="7">G450*H450</f>
         <v>1305</v>
       </c>
     </row>
@@ -17095,6 +17149,296 @@
       <c r="I501" s="3">
         <f t="shared" si="7"/>
         <v>336</v>
+      </c>
+    </row>
+    <row r="502" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A502" s="5">
+        <v>100501</v>
+      </c>
+      <c r="B502" s="2">
+        <v>46077</v>
+      </c>
+      <c r="C502" t="s">
+        <v>117</v>
+      </c>
+      <c r="D502" t="s">
+        <v>19</v>
+      </c>
+      <c r="E502" t="s">
+        <v>40</v>
+      </c>
+      <c r="F502" t="s">
+        <v>21</v>
+      </c>
+      <c r="G502" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="H502" s="4">
+        <v>7</v>
+      </c>
+      <c r="I502" s="6" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="503" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A503" s="5">
+        <v>100502</v>
+      </c>
+      <c r="B503" s="2">
+        <v>46011</v>
+      </c>
+      <c r="C503" t="s">
+        <v>81</v>
+      </c>
+      <c r="D503" t="s">
+        <v>16</v>
+      </c>
+      <c r="E503" t="s">
+        <v>37</v>
+      </c>
+      <c r="F503" t="s">
+        <v>13</v>
+      </c>
+      <c r="G503" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="H503" s="4">
+        <v>1</v>
+      </c>
+      <c r="I503" s="6" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="504" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A504" s="5">
+        <v>100503</v>
+      </c>
+      <c r="B504" s="2">
+        <v>45978</v>
+      </c>
+      <c r="C504" t="s">
+        <v>69</v>
+      </c>
+      <c r="D504" t="s">
+        <v>19</v>
+      </c>
+      <c r="E504" t="s">
+        <v>114</v>
+      </c>
+      <c r="F504" t="s">
+        <v>21</v>
+      </c>
+      <c r="G504" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="H504" s="4">
+        <v>9</v>
+      </c>
+      <c r="I504" s="6" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="505" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A505" s="5">
+        <v>100504</v>
+      </c>
+      <c r="B505" s="2">
+        <v>45961</v>
+      </c>
+      <c r="C505" t="s">
+        <v>71</v>
+      </c>
+      <c r="D505" t="s">
+        <v>36</v>
+      </c>
+      <c r="E505" t="s">
+        <v>49</v>
+      </c>
+      <c r="F505" t="s">
+        <v>24</v>
+      </c>
+      <c r="G505" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="H505" s="4">
+        <v>8</v>
+      </c>
+      <c r="I505" s="6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="506" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A506" s="5">
+        <v>100505</v>
+      </c>
+      <c r="B506" s="2">
+        <v>45985</v>
+      </c>
+      <c r="C506" t="s">
+        <v>159</v>
+      </c>
+      <c r="D506" t="s">
+        <v>36</v>
+      </c>
+      <c r="E506" t="s">
+        <v>49</v>
+      </c>
+      <c r="F506" t="s">
+        <v>24</v>
+      </c>
+      <c r="G506" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="H506" s="4">
+        <v>8</v>
+      </c>
+      <c r="I506" s="6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="507" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A507" s="5">
+        <v>100506</v>
+      </c>
+      <c r="B507" s="2">
+        <v>45982</v>
+      </c>
+      <c r="C507" t="s">
+        <v>10</v>
+      </c>
+      <c r="D507" t="s">
+        <v>16</v>
+      </c>
+      <c r="E507" t="s">
+        <v>51</v>
+      </c>
+      <c r="F507" t="s">
+        <v>21</v>
+      </c>
+      <c r="G507" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="H507" s="4">
+        <v>8</v>
+      </c>
+      <c r="I507" s="6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="508" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A508" s="5">
+        <v>100507</v>
+      </c>
+      <c r="B508" s="2">
+        <v>45975</v>
+      </c>
+      <c r="C508" t="s">
+        <v>184</v>
+      </c>
+      <c r="D508" t="s">
+        <v>11</v>
+      </c>
+      <c r="E508" t="s">
+        <v>64</v>
+      </c>
+      <c r="F508" t="s">
+        <v>65</v>
+      </c>
+      <c r="G508" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="H508" s="4">
+        <v>6</v>
+      </c>
+      <c r="I508" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="509" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A509" s="5">
+        <v>100508</v>
+      </c>
+      <c r="B509" s="2">
+        <v>46019</v>
+      </c>
+      <c r="C509" t="s">
+        <v>58</v>
+      </c>
+      <c r="D509" t="s">
+        <v>19</v>
+      </c>
+      <c r="E509" t="s">
+        <v>43</v>
+      </c>
+      <c r="F509" t="s">
+        <v>21</v>
+      </c>
+      <c r="G509" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="H509" s="4">
+        <v>5</v>
+      </c>
+      <c r="I509" s="6" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="510" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A510" s="5">
+        <v>100509</v>
+      </c>
+      <c r="B510" s="2">
+        <v>46007</v>
+      </c>
+      <c r="C510" t="s">
+        <v>32</v>
+      </c>
+      <c r="D510" t="s">
+        <v>16</v>
+      </c>
+      <c r="E510" t="s">
+        <v>40</v>
+      </c>
+      <c r="F510" t="s">
+        <v>21</v>
+      </c>
+      <c r="G510" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="H510" s="4">
+        <v>9</v>
+      </c>
+      <c r="I510" s="6" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="511" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A511" s="5">
+        <v>100510</v>
+      </c>
+      <c r="B511" s="2">
+        <v>45988</v>
+      </c>
+      <c r="C511" t="s">
+        <v>10</v>
+      </c>
+      <c r="D511" t="s">
+        <v>16</v>
+      </c>
+      <c r="E511" t="s">
+        <v>74</v>
+      </c>
+      <c r="F511" t="s">
+        <v>21</v>
+      </c>
+      <c r="G511" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="H511" s="4">
+        <v>4</v>
+      </c>
+      <c r="I511" s="6" t="s">
+        <v>599</v>
       </c>
     </row>
   </sheetData>

--- a/data/sales-tracker.xlsx
+++ b/data/sales-tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/realdekings/Documents/Projects/data-engineering/small-business-sales-tracker-pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47518805-88DA-5D44-ADD5-5E4CC499B7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD050880-FE4F-E34A-8739-8660082F1F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SalesTracker" sheetId="1" r:id="rId1"/>
@@ -1790,9 +1790,6 @@
     <t>$15.00</t>
   </si>
   <si>
-    <t>$105.00</t>
-  </si>
-  <si>
     <t>$25.00</t>
   </si>
   <si>
@@ -1833,6 +1830,9 @@
   </si>
   <si>
     <t>$168.00</t>
+  </si>
+  <si>
+    <t>$100.00</t>
   </si>
 </sst>
 </file>
@@ -17174,10 +17174,10 @@
         <v>584</v>
       </c>
       <c r="H502" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I502" s="6" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.2">
@@ -17200,13 +17200,13 @@
         <v>13</v>
       </c>
       <c r="G503" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H503" s="4">
         <v>1</v>
       </c>
       <c r="I503" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.2">
@@ -17229,13 +17229,13 @@
         <v>21</v>
       </c>
       <c r="G504" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H504" s="4">
         <v>9</v>
       </c>
       <c r="I504" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="505" spans="1:9" x14ac:dyDescent="0.2">
@@ -17258,13 +17258,13 @@
         <v>24</v>
       </c>
       <c r="G505" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H505" s="4">
         <v>8</v>
       </c>
       <c r="I505" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="506" spans="1:9" x14ac:dyDescent="0.2">
@@ -17287,13 +17287,13 @@
         <v>24</v>
       </c>
       <c r="G506" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H506" s="4">
         <v>8</v>
       </c>
       <c r="I506" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="507" spans="1:9" x14ac:dyDescent="0.2">
@@ -17316,13 +17316,13 @@
         <v>21</v>
       </c>
       <c r="G507" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H507" s="4">
         <v>8</v>
       </c>
       <c r="I507" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="508" spans="1:9" x14ac:dyDescent="0.2">
@@ -17345,13 +17345,13 @@
         <v>65</v>
       </c>
       <c r="G508" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H508" s="4">
         <v>6</v>
       </c>
       <c r="I508" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.2">
@@ -17374,13 +17374,13 @@
         <v>21</v>
       </c>
       <c r="G509" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H509" s="4">
         <v>5</v>
       </c>
       <c r="I509" s="6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.2">
@@ -17409,7 +17409,7 @@
         <v>9</v>
       </c>
       <c r="I510" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.2">
@@ -17432,13 +17432,13 @@
         <v>21</v>
       </c>
       <c r="G511" s="6" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H511" s="4">
         <v>4</v>
       </c>
       <c r="I511" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
